--- a/Scraped Tweets - Nigeria/_summary.xlsx
+++ b/Scraped Tweets - Nigeria/_summary.xlsx
@@ -14,42 +14,39 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>creator</t>
   </si>
   <si>
-    <t>orientation</t>
-  </si>
-  <si>
-    <t>raw_scraped</t>
-  </si>
-  <si>
-    <t>quality_passed</t>
-  </si>
-  <si>
-    <t>llm_scope_relevant</t>
-  </si>
-  <si>
     <t>final_selected</t>
   </si>
   <si>
+    <t>path</t>
+  </si>
+  <si>
+    <t>Agba John Doe</t>
+  </si>
+  <si>
     <t>Deyemi Okanlawon</t>
   </si>
   <si>
-    <t>Agba John Doe</t>
-  </si>
-  <si>
     <t>Shola</t>
   </si>
   <si>
     <t>Wizarab</t>
   </si>
   <si>
-    <t>Progressive</t>
-  </si>
-  <si>
-    <t>Regressive</t>
+    <t>Scraped Tweets - Nigeria/Agba John Doe_scope_relevant.xlsx</t>
+  </si>
+  <si>
+    <t>Scraped Tweets - Nigeria/Deyemi Okanlawon_scope_relevant.xlsx</t>
+  </si>
+  <si>
+    <t>Scraped Tweets - Nigeria/Shola_scope_relevant.xlsx</t>
+  </si>
+  <si>
+    <t>Scraped Tweets - Nigeria/Wizarab_scope_relevant.xlsx</t>
   </si>
 </sst>
 </file>
@@ -407,10 +404,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -420,94 +417,49 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="B2">
+        <v>120</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="B3">
+        <v>138</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
         <v>5</v>
       </c>
+      <c r="B4">
+        <v>144</v>
+      </c>
+      <c r="C4" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="2" spans="1:6">
-      <c r="A2" t="s">
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
         <v>6</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B5">
+        <v>100</v>
+      </c>
+      <c r="C5" t="s">
         <v>10</v>
-      </c>
-      <c r="C2">
-        <v>400</v>
-      </c>
-      <c r="D2">
-        <v>279</v>
-      </c>
-      <c r="E2">
-        <v>21</v>
-      </c>
-      <c r="F2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3">
-        <v>400</v>
-      </c>
-      <c r="D3">
-        <v>247</v>
-      </c>
-      <c r="E3">
-        <v>61</v>
-      </c>
-      <c r="F3">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4">
-        <v>400</v>
-      </c>
-      <c r="D4">
-        <v>261</v>
-      </c>
-      <c r="E4">
-        <v>61</v>
-      </c>
-      <c r="F4">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5">
-        <v>400</v>
-      </c>
-      <c r="D5">
-        <v>265</v>
-      </c>
-      <c r="E5">
-        <v>39</v>
-      </c>
-      <c r="F5">
-        <v>39</v>
       </c>
     </row>
   </sheetData>
